--- a/results/Int Task Remove ACC 0.4/Rando_10_permute.xlsx
+++ b/results/Int Task Remove ACC 0.4/Rando_10_permute.xlsx
@@ -440,657 +440,657 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.6068552528863141</v>
+        <v>0.628877521673035</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>hrv_lineintegral</t>
+          <t>bvp_energy</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.6126946464521961</v>
+        <v>0.6588448580467563</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>scl_svd_entropy</t>
+          <t>hrv_max</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.6112977114918443</v>
+        <v>0.6098494186285386</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>bvp_svd_entropy</t>
+          <t>scl_sum</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.6037275565964091</v>
+        <v>0.6296530260076421</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>bvp_lineintegral</t>
+          <t>scr_mean</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.6235054850240355</v>
+        <v>0.6251540737088623</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>bvp_max</t>
+          <t>scl_energy</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.6523686264842434</v>
+        <v>0.6840359094457455</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>scl_n_sign_changes</t>
+          <t>scr_sum</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.6506892230576441</v>
+        <v>0.6762141008258351</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>scl_pct_5</t>
+          <t>scl_mean</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.6808414478820001</v>
+        <v>0.7006912773737622</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>bvp_entropy</t>
+          <t>hrv_n_below_mean</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.6808414478820001</v>
+        <v>0.6909024610707095</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>
-          <t>scr_n_below_mean</t>
+          <t>scl_pct_95</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.6750636837996631</v>
+        <v>0.7014667817083693</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
         <is>
-          <t>hrv_pct_95</t>
+          <t>hrv_iqr_5_95</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.649199843871975</v>
+        <v>0.6792955750030815</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>bvp_pct_95</t>
+          <t>hrv_min</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.6556041743703521</v>
+        <v>0.6120732158264514</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>scr_iqr_5_95</t>
+          <t>scl_iqr</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.6535806729939603</v>
+        <v>0.6062389580508649</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="inlineStr">
         <is>
-          <t>bvp_n_sign_changes</t>
+          <t>bvp_peaks</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.6204034676856075</v>
+        <v>0.577689099798677</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>hrv_entropy</t>
+          <t>scr_pct_95</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.6167313776243889</v>
+        <v>0.573698590739143</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="inlineStr">
         <is>
-          <t>scr_min</t>
+          <t>scr_n_above_mean</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>0.6167313776243889</v>
+        <v>0.5784800115041703</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="inlineStr">
         <is>
-          <t>scl_sum</t>
+          <t>scr_kurtosis</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>0.6230946218004026</v>
+        <v>0.5787932947121903</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>bvp_sum</t>
+          <t>scl_entropy</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>0.6234079050084227</v>
+        <v>0.5806421792185381</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="1" t="inlineStr">
         <is>
-          <t>scl_perm_entropy</t>
+          <t>hrv_perm_entropy</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>0.6244350630675048</v>
+        <v>0.5755474752454908</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="1" t="inlineStr">
         <is>
-          <t>hrv_std</t>
+          <t>bvp_rms</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0.6182875220838983</v>
+        <v>0.5857522905624718</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="1" t="inlineStr">
         <is>
-          <t>hrv_iqr</t>
+          <t>scl_n_sign_changes</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0.6087863100373886</v>
+        <v>0.5860090800772423</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="1" t="inlineStr">
         <is>
-          <t>scr_mean</t>
+          <t>hrv_skewness</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>0.6024641521837381</v>
+        <v>0.5866356464932824</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
         <is>
-          <t>scr_perm_entropy</t>
+          <t>bvp_entropy</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0.6061927359382062</v>
+        <v>0.5866356464932824</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="inlineStr">
         <is>
-          <t>scl_std</t>
+          <t>bvp_min</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>0.5929064464439788</v>
+        <v>0.6338232877275155</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="1" t="inlineStr">
         <is>
-          <t>scr_kurtosis</t>
+          <t>hrv_sum</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>0.5926496569292082</v>
+        <v>0.6048420230905132</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="1" t="inlineStr">
         <is>
-          <t>hrv_skewness</t>
+          <t>bvp_n_above_mean</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>0.5937589876330169</v>
+        <v>0.5932813591355438</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="1" t="inlineStr">
         <is>
-          <t>bvp_energy</t>
+          <t>bvp_iqr_5_95</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>0.5867332265088951</v>
+        <v>0.5640124902419985</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="1" t="inlineStr">
         <is>
-          <t>bvp_std</t>
+          <t>scr_std</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>0.5932145938617035</v>
+        <v>0.5807448950244464</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="1" t="inlineStr">
         <is>
-          <t>bvp_iqr</t>
+          <t>bvp_lineintegral</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>0.6318973663667364</v>
+        <v>0.5316518755906159</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="1" t="inlineStr">
         <is>
-          <t>bvp_pct_5</t>
+          <t>scl_n_below_mean</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>0.6282509552569949</v>
+        <v>0.5294897078762481</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="1" t="inlineStr">
         <is>
-          <t>scr_pct_95</t>
+          <t>scr_iqr</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>0.6197614938986812</v>
+        <v>0.5011350096552858</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="1" t="inlineStr">
         <is>
-          <t>scl_n_below_mean</t>
+          <t>scl_min</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>0.6096850733390854</v>
+        <v>0.4980329923168577</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="1" t="inlineStr">
         <is>
-          <t>scr_rms</t>
+          <t>scl_iqr_5_95</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>0.6447573852664448</v>
+        <v>0.5121153293068738</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="1" t="inlineStr">
         <is>
-          <t>hrv_kurtosis</t>
+          <t>scl_skewness</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>0.6491690291302026</v>
+        <v>0.513794732733473</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="1" t="inlineStr">
         <is>
-          <t>scr_max</t>
+          <t>hrv_std</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>0.6605756193763096</v>
+        <v>0.5070514400755988</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="1" t="inlineStr">
         <is>
-          <t>scr_svd_entropy</t>
+          <t>bvp_mean</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>0.6634259829902626</v>
+        <v>0.5108930112165661</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="1" t="inlineStr">
         <is>
-          <t>scr_pct_5</t>
+          <t>bvp_n_sign_changes</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>0.6392877686018325</v>
+        <v>0.4808435021981182</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="1" t="inlineStr">
         <is>
-          <t>bvp_n_above_mean</t>
+          <t>bvp_sum</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>0.6217490447430051</v>
+        <v>0.4811567854061383</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="1" t="inlineStr">
         <is>
-          <t>scr_skewness</t>
+          <t>bvp_svd_entropy</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>0.6303720366489995</v>
+        <v>0.4699710341427339</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="1" t="inlineStr">
         <is>
-          <t>scl_lineintegral</t>
+          <t>scr_iqr_5_95</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>0.6372539956448497</v>
+        <v>0.4628220140515223</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="1" t="inlineStr">
         <is>
-          <t>scl_mean</t>
+          <t>scl_perm_entropy</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>0.6644890915814126</v>
+        <v>0.4621389539422326</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="1" t="inlineStr">
         <is>
-          <t>hrv_rms</t>
+          <t>scr_svd_entropy</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>0.6323955380253914</v>
+        <v>0.470910883766794</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="1" t="inlineStr">
         <is>
-          <t>hrv_perm_entropy</t>
+          <t>scr_pct_5</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>0.6314556884013311</v>
+        <v>0.4646503553966885</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="1" t="inlineStr">
         <is>
-          <t>scl_max</t>
+          <t>scr_perm_entropy</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>0.6319076379473274</v>
+        <v>0.4652769218127286</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="1" t="inlineStr">
         <is>
-          <t>scl_pct_95</t>
+          <t>scr_n_sign_changes</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>0.6414345289453141</v>
+        <v>0.4652769218127286</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="1" t="inlineStr">
         <is>
-          <t>scl_iqr_5_95</t>
+          <t>bvp_n_below_mean</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>0.643571017708205</v>
+        <v>0.4958451456510128</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="1" t="inlineStr">
         <is>
-          <t>hrv_peaks</t>
+          <t>scr_energy</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>0.6429495870824602</v>
+        <v>0.4772484489913308</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="1" t="inlineStr">
         <is>
-          <t>bvp_peaks</t>
+          <t>scr_peaks</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>0.5757939931796705</v>
+        <v>0.4772484489913308</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="1" t="inlineStr">
         <is>
-          <t>hrv_iqr_5_95</t>
+          <t>scl_std</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>0.5983452483668187</v>
+        <v>0.4813981675500226</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="1" t="inlineStr">
         <is>
-          <t>scl_kurtosis</t>
+          <t>scr_n_below_mean</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>0.5969226344549899</v>
+        <v>0.4874327211471301</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="1" t="inlineStr">
         <is>
-          <t>bvp_ptp</t>
+          <t>scl_lineintegral</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>0.583379555445992</v>
+        <v>0.4672644726570525</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="1" t="inlineStr">
         <is>
-          <t>scl_ptp</t>
+          <t>scl_n_above_mean</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>0.5920898557870085</v>
+        <v>0.4733503841571141</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="1" t="inlineStr">
         <is>
-          <t>bvp_perm_entropy</t>
+          <t>scl_ptp</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>0.4955215908624019</v>
+        <v>0.4765140309790871</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="1" t="inlineStr">
         <is>
-          <t>scr_n_sign_changes</t>
+          <t>hrv_kurtosis</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>0.4955215908624019</v>
+        <v>0.476601339414109</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="1" t="inlineStr">
         <is>
-          <t>bvp_iqr_5_95</t>
+          <t>scl_rms</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>0.5201220263774189</v>
+        <v>0.5006317022063356</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="1" t="inlineStr">
         <is>
-          <t>scr_std</t>
+          <t>scr_skewness</t>
         </is>
       </c>
       <c r="B57" t="n">
-        <v>0.520835901228481</v>
+        <v>0.5003184189983154</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="1" t="inlineStr">
         <is>
-          <t>scr_n_above_mean</t>
+          <t>bvp_pct_95</t>
         </is>
       </c>
       <c r="B58" t="n">
-        <v>0.5175387238588274</v>
+        <v>0.5673712970951971</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="1" t="inlineStr">
         <is>
-          <t>scr_peaks</t>
+          <t>bvp_perm_entropy</t>
         </is>
       </c>
       <c r="B59" t="n">
-        <v>0.5175387238588274</v>
+        <v>0.5016485886848268</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="1" t="inlineStr">
         <is>
-          <t>hrv_pct_5</t>
+          <t>hrv_energy</t>
         </is>
       </c>
       <c r="B60" t="n">
-        <v>0.4984130407987181</v>
+        <v>0.4887526192530506</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="1" t="inlineStr">
         <is>
-          <t>hrv_max</t>
+          <t>scl_svd_entropy</t>
         </is>
       </c>
       <c r="B61" t="n">
-        <v>0.4948385307531123</v>
+        <v>0.4846850733390854</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="1" t="inlineStr">
         <is>
-          <t>hrv_mean</t>
+          <t>hrv_iqr</t>
         </is>
       </c>
       <c r="B62" t="n">
-        <v>0.4982332881383787</v>
+        <v>0.4744134927482641</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="1" t="inlineStr">
         <is>
-          <t>scl_n_above_mean</t>
+          <t>bvp_skewness</t>
         </is>
       </c>
       <c r="B63" t="n">
-        <v>0.4982332881383787</v>
+        <v>0.4684354328444061</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="1" t="inlineStr">
         <is>
-          <t>bvp_mean</t>
+          <t>bvp_kurtosis</t>
         </is>
       </c>
       <c r="B64" t="n">
-        <v>0.4982332881383787</v>
+        <v>0.4734171494309544</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="1" t="inlineStr">
         <is>
-          <t>bvp_skewness</t>
+          <t>scr_max</t>
         </is>
       </c>
       <c r="B65" t="n">
-        <v>0.4984900776531492</v>
+        <v>0.4709673774600436</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="1" t="inlineStr">
         <is>
-          <t>bvp_min</t>
+          <t>bvp_max</t>
         </is>
       </c>
       <c r="B66" t="n">
-        <v>0.4992296314556884</v>
+        <v>0.4537162578577592</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="1" t="inlineStr">
         <is>
-          <t>scl_skewness</t>
+          <t>bvp_pct_5</t>
         </is>
       </c>
       <c r="B67" t="n">
-        <v>0.4982897818316282</v>
+        <v>0.4418320391141789</v>
       </c>
     </row>
     <row r="68">
@@ -1100,97 +1100,97 @@
         </is>
       </c>
       <c r="B68" t="n">
-        <v>0.4985465713463988</v>
+        <v>0.4391562923702699</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="1" t="inlineStr">
         <is>
-          <t>scr_ptp</t>
+          <t>hrv_mean</t>
         </is>
       </c>
       <c r="B69" t="n">
-        <v>0.4981767944451292</v>
+        <v>0.5019567361025514</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="1" t="inlineStr">
         <is>
-          <t>scl_entropy</t>
+          <t>hrv_entropy</t>
         </is>
       </c>
       <c r="B70" t="n">
-        <v>0.4966103784050289</v>
+        <v>0.4971188216442746</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="1" t="inlineStr">
         <is>
-          <t>hrv_n_below_mean</t>
+          <t>hrv_pct_5</t>
         </is>
       </c>
       <c r="B71" t="n">
-        <v>0.4966103784050289</v>
+        <v>0.5003697769012696</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="1" t="inlineStr">
         <is>
-          <t>hrv_ptp</t>
+          <t>hrv_rms</t>
         </is>
       </c>
       <c r="B72" t="n">
-        <v>0.496923661613049</v>
+        <v>0.49968671679198</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="1" t="inlineStr">
         <is>
-          <t>scr_lineintegral</t>
+          <t>scr_min</t>
         </is>
       </c>
       <c r="B73" t="n">
-        <v>0.4986595587328978</v>
+        <v>0.49968671679198</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="1" t="inlineStr">
         <is>
-          <t>scl_min</t>
+          <t>hrv_n_above_mean</t>
         </is>
       </c>
       <c r="B74" t="n">
-        <v>0.5094703973047373</v>
+        <v>0.49968671679198</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="1" t="inlineStr">
         <is>
-          <t>hrv_sum</t>
+          <t>scr_lineintegral</t>
         </is>
       </c>
       <c r="B75" t="n">
-        <v>0.5032663626278812</v>
+        <v>0.49968671679198</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="1" t="inlineStr">
         <is>
-          <t>bvp_n_below_mean</t>
+          <t>bvp_iqr</t>
         </is>
       </c>
       <c r="B76" t="n">
-        <v>0.507991289699659</v>
+        <v>0.4974937343358396</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="1" t="inlineStr">
         <is>
-          <t>hrv_energy</t>
+          <t>hrv_peaks</t>
         </is>
       </c>
       <c r="B77" t="n">
-        <v>0.5014482928633058</v>
+        <v>0.4974937343358396</v>
       </c>
     </row>
     <row r="78">
@@ -1200,127 +1200,127 @@
         </is>
       </c>
       <c r="B78" t="n">
-        <v>0.5014482928633058</v>
+        <v>0.4978070175438596</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="1" t="inlineStr">
         <is>
-          <t>scr_energy</t>
+          <t>scr_ptp</t>
         </is>
       </c>
       <c r="B79" t="n">
-        <v>0.4989728419409178</v>
+        <v>0.4978635112371091</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="1" t="inlineStr">
         <is>
-          <t>hrv_n_sign_changes</t>
+          <t>scl_peaks</t>
         </is>
       </c>
       <c r="B80" t="n">
-        <v>0.4989728419409178</v>
+        <v>0.4978635112371091</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="1" t="inlineStr">
         <is>
-          <t>hrv_n_above_mean</t>
+          <t>bvp_std</t>
         </is>
       </c>
       <c r="B81" t="n">
-        <v>0.5006522453675172</v>
+        <v>0.4984027692181273</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="1" t="inlineStr">
         <is>
-          <t>scl_rms</t>
+          <t>hrv_pct_95</t>
         </is>
       </c>
       <c r="B82" t="n">
-        <v>0.505289864004273</v>
+        <v>0.4990601503759399</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="1" t="inlineStr">
         <is>
-          <t>bvp_kurtosis</t>
+          <t>scl_pct_5</t>
         </is>
       </c>
       <c r="B83" t="n">
-        <v>0.511180615473109</v>
+        <v>0.4987468671679198</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="1" t="inlineStr">
         <is>
-          <t>scr_sum</t>
+          <t>scr_rms</t>
         </is>
       </c>
       <c r="B84" t="n">
-        <v>0.5131733021077284</v>
+        <v>0.49968671679198</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="1" t="inlineStr">
         <is>
-          <t>bvp_rms</t>
+          <t>hrv_n_sign_changes</t>
         </is>
       </c>
       <c r="B85" t="n">
-        <v>0.5148783844858047</v>
+        <v>0.49968671679198</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="1" t="inlineStr">
         <is>
-          <t>scl_energy</t>
+          <t>bvp_ptp</t>
         </is>
       </c>
       <c r="B86" t="n">
-        <v>0.5138204116849501</v>
+        <v>0.4990601503759399</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="1" t="inlineStr">
         <is>
-          <t>hrv_min</t>
+          <t>hrv_lineintegral</t>
         </is>
       </c>
       <c r="B87" t="n">
-        <v>0.4993734335839599</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="1" t="inlineStr">
         <is>
-          <t>scr_iqr</t>
+          <t>hrv_ptp</t>
         </is>
       </c>
       <c r="B88" t="n">
-        <v>0.5</v>
+        <v>0.49968671679198</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="1" t="inlineStr">
         <is>
-          <t>scl_iqr</t>
+          <t>scl_kurtosis</t>
         </is>
       </c>
       <c r="B89" t="n">
-        <v>0.5</v>
+        <v>0.49968671679198</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="1" t="inlineStr">
         <is>
-          <t>scl_peaks</t>
+          <t>scl_max</t>
         </is>
       </c>
       <c r="B90" t="n">
-        <v>0.5</v>
+        <v>0.49968671679198</v>
       </c>
     </row>
   </sheetData>
